--- a/www/download/COUNTRY.IND.EXI382.xlsx
+++ b/www/download/COUNTRY.IND.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Índia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.181</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>185.241</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>80.1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>85.691</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>86.944</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>87.672</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>88.673</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>85.797</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>90.799</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>89.891</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>91.222</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>96.95</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>95.355</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>98.017</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>98.831</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>104.641</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>107.069</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>109.588</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>104.269</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>113.01</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>111.079</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>104.771</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>129.917</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>138.068</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>127.868</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>124.245</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>138.278</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>145.559</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>71.506</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>31.866</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>33.174</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>34.527</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>33.343</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>34.089</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>31.281</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>33.667</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>32.707</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>35.326</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>34.961</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>36.656</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>35.429</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>39.922</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>41.051</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>43.109</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>40.647</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>47.082</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>44.266</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>42.684</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>49.866</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>52.814</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>52.404</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>51.112</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>57.265</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>60.435</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>400443.019</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>159748.684</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>171293.068</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>175564.396</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>174715.623</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>177777.422</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>170126.99</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>183341.336</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>179586.988</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>182376.093</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>198460.272</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>193845.386</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>201335.393</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>211094.576</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>222632.673</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>219844.436</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>228328.637</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>221567.196</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>238960.696</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>234290.15</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>224315.049</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>276364.455</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>293791.174</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>263959.634</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>257941.521</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>286545.049</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>301526.123</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>160644.883</t>
+          <t>421243436191.943</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-24870.244</t>
+          <t>211025823405.305</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-30795.088</t>
+          <t>230503967916.115</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-28501.217</t>
+          <t>218730521365.515</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-33981.239</t>
+          <t>228183654120.23</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-33487.158</t>
+          <t>213436119737.708</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-39323.505</t>
+          <t>232075820868.954</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-41397.884</t>
+          <t>249891943760.54</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-44035.325</t>
+          <t>256961285066.19</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-46045.971</t>
+          <t>247443553149.183</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-47202.77</t>
+          <t>274640316447.368</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-45180.136</t>
+          <t>286333520091.803</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-44497.813</t>
+          <t>274545067274.857</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-53237.904</t>
+          <t>285719105334.514</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-47949.677</t>
+          <t>325138549861.16</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>-45485.336</t>
+          <t>306780256825.065</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-41719.771</t>
+          <t>311415304130.989</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>-40200.173</t>
+          <t>290276720557.899</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>-32977.008</t>
+          <t>300717592631.435</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>97708.111</t>
+          <t>305894427326.011</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>95205.135</t>
+          <t>265767367436.847</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>111099.72</t>
+          <t>325847750476.461</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>117822.911</t>
+          <t>338692724081.579</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>115894.177</t>
+          <t>363640780999.9</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>113474.093</t>
+          <t>343932281936.628</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>127061.319</t>
+          <t>392014148587.66</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>134139.702</t>
+          <t>412664893501.831</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>82673637731.9589</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>31859534377.5953</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>33617196778.6392</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>22997540796.6766</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>28247607176.96</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>34139264865.3433</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>31586500954.4301</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32529893177.084</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>31253579696.7359</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>40528754287.8399</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>42788542267.3231</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>42111143739.2909</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>42092327275.2458</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>44857653298.6015</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>45044112911.0295</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>48048363096.9515</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>44720839173.8252</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>46054175456.6114</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>44295651035.6951</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>42438227753.0193</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>46338366995.795</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>61912797441.1127</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>62690674108.5169</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>67495610783.134</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>66387432172.9175</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>76017407907.734</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>78635133835.7937</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>222392067.462186</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>58078615.1123888</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>63717950.2412963</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>126930634.298334</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>91908001.6040623</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>68402227.1733711</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>72485940.4665161</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>67517388.6052821</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>159399213.133763</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>68360038.5429168</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>77527350.9543626</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>57531244.6898477</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>50044861.0391757</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>47530747.951884</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>43536735.68531</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>29653705.7278062</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>27835437.547907</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>24932064.0509706</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>28520439.321036</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>11142021264.3345</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>9513336179.5119</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>10017399501.4463</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>387177445.783488</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>425392701.104201</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>366356870.55283</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>390030111.999876</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>390931466.302454</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>850036.293592379</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>807568.827385464</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>933874.963095589</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>961116.542237862</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1021614.82932858</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1236125.97353736</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1241857.42408611</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1235823.64030302</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1108723.36336616</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1116821.27975516</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1273408.21384642</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1377511.60334706</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1417796.31212618</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1460820.54975555</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1556892.72138201</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1738315.10885542</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1860480.39624225</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1910718.7841049</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2039797.44503791</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2091084.04593653</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2208198.09722412</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2482651.29859679</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2798922.99075738</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2878530.72557742</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2958997.90698694</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3156264.23907101</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3265143.8035184</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1570228.145479</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1603600.51657868</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1907794.67729482</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1861165.10576569</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2048015.57488022</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2289916.31632019</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2500095.1432129</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2609530.78536285</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2464973.47477027</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2319640.2360617</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2760072.50094766</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3078174.0761454</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3057858.84033321</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3197628.08987601</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3646477.315549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3967699.4214132</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>4192992.43312576</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4313903.68435448</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>4365511.05198908</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>4596442.72420225</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>4511174.39959203</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5041333.19413201</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>5540027.58993698</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5784962.89019171</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>5829607.72088853</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>6321015.28985574</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>6532757.68947555</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.943121013735968</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-1.78062170354416</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-1.91605163282007</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-2.23931585780956</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-2.20297761106103</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1.98089862602888</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.24494653766339</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-2.27261051165013</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-2.40896900218817</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-2.13613092258017</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-2.10316377933929</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-2.07287838771751</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-2.05714784333409</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-2.18681874964773</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-2.0645048575988</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-1.94665734831098</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-1.93289329473079</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-1.87288877938738</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-1.74447507213545</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.30236078252673</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.05456388285958</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.794454857202776</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.879432825168461</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.717062423610419</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.70927070103545</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.671476611533426</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.705849482896229</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1156.17697038734</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>999.803374701987</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1013.36892715102</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>666.074110020651</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>847.182532374731</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1001.48627005442</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1009.76311429124</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>966.239234166224</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>956.360667225881</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1239.14997409816</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1211.23072671584</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1204.51082169104</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1148.29721699183</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1266.1388450208</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1128.30301365459</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1170.4667677678</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1037.37782098735</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1133.01372671423</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>940.821229298297</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>958.699810854352</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1085.60521833018</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1241.59232341476</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1187.00105586808</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1287.99739388384</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1298.85443017949</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1327.46225542868</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1301.15017036523</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-21364557862.2988</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-18153433635.5718</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>-23002771249.1766</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-43326135097.1371</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-29837272712.6121</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>-21810962114.9964</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>-28729874972.4206</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-23826375692.1202</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>-18480871266.6269</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-10840032601.1335</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>-12288358519.3003</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>-15950538016.1977</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>-13531837455.4151</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>-6993465855.76585</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-9333370805.18861</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>-2540128026.72656</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>347435581.241432</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>-688912093.163516</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>-165652374.96647</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>-8722262922.50325</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>-3887298536.34355</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>-5337608761.03688</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>-11011898885.1396</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>-8863915302.59277</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>-8853176466.4956</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>-7209873278.243</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>-7489001912.15141</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-17129571546.4576</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-17008766694.5644</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-21890946734.3132</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-42290557254.5035</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-28592755320.5743</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-20825661280.6478</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-27665994517.4588</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-22860456353.5251</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-17640612460.3845</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-9935743561.30457</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-11477825623.788</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-15451807000.0569</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-12976878784.5416</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-6656494322.00219</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-8694215730.0915</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-1978687109.66722</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>744305696.168155</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-96863116.1601324</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>681967634.858773</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-8250964241.57698</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-3444105398.35335</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-4820351724.43396</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-10193053621.1898</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-7816122370.61367</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-8052359829.25372</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-6327690606.81257</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-5439753457.42134</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-4234986315.84121</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-1144666941.00741</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-1111824514.8634</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-1035577842.63356</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-1244517392.03786</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-985300834.348608</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1063880454.96175</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-965919338.595073</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-840258806.24235</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-904289039.828982</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-810532895.512298</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-498731016.140783</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-554958670.873518</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-336971533.76366</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-639155075.097104</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-561440917.059334</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-396870114.926723</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-592048977.003384</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-847620009.825244</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-471298680.926272</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-443193137.990198</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-517257036.602925</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-818845263.949845</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-1047792931.9791</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-800816637.241879</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-882182671.430429</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-2049248454.73007</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>2246.59176675723</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>-780.46821356907</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>-928.298260365813</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-825.476207024982</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1019.14161892878</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>-982.356506283165</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>-1257.10109299707</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>-1229.64620616871</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>-1347.48253503326</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>-1407.83660328734</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>-1336.18586613572</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1292.29362836418</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>-1213.91992644946</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>-1502.67732092801</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>-1201.08403887868</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>-1108.03096666119</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.155</t>
+          <t>-967.762813301541</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>-988.994968940726</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>-700.41795254841</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>2207.27284672685</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>1.383</t>
+          <t>2230.44527262507</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>2227.9813754173</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1.568</t>
+          <t>2230.88874790809</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.554</t>
+          <t>2211.57192674609</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>2220.09382241589</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1.829</t>
+          <t>2218.82211264246</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1.949</t>
+          <t>2219.56634528787</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2161.74184373341</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>1994.36808285679</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>1998.95051434552</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2019.29062058587</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1992.83036450602</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>2004.86757509935</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>1982.89213892293</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>2019.20217095057</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1997.83724011529</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>1999.26435186407</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>2047.04369379186</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>2032.87479563295</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>2054.09065588815</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>2135.9059570145</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>2127.57938787113</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>2053.30447955826</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>2083.52050728231</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>2124.94937153209</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>2114.51304223102</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>2109.22308594503</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>2141.00281299817</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>2127.2388107569</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>2127.86991925866</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>2064.31487697523</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>2076.07521354066</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>2072.24141257863</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>2071.49967481589</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>58699.7207307428</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>66375.395403715</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>76651.5829565725</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>65719.448102232</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>68709.1340066191</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>94499.8882849485</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>90523.0846679869</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>85533.769705538</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>73362.2870103219</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>79887.8812278651</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>95905.8929932121</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>110343.175692356</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>113371.310201373</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>125954.588590589</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>111375.741889893</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>162021.20533338</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>196351.819869394</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>202122.231325965</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>188983.243233097</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>180443.080513637</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>190665.205891708</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>187047.087801949</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>212646.764252927</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>218289.146821109</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>215747.022287329</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>223747.478492011</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>236862.797853312</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>60024252868.7512</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>35356024086.6135</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>39625924781.3232</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>58387344870.517</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>48182023024.7665</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>41697476395.2998</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>49334517029.2668</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>46798978580.7604</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>39725203844.9872</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>39063804239.85</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>42815560422.1966</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>45185473246.1257</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>38619586123.5216</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>44256031676.9525</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>41632967581.8079</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>38377944603.3997</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>41715368119.4373</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>41527664106.6679</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>41350879994.8497</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>40533552867.8921</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>34723030992.3068</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>37153324740.4235</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>43566698582.7625</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>47325593657.233</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>41002674682.1531</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>44767223416.8102</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>45600046629.419</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>58146.4440583725</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>63930.8666819268</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>72758.593597552</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>49803.6378755429</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>51162.2699025896</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>68133.4912181563</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>69541.885135663</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>67298.4851490452</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>53547.2388407393</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>66323.6656690913</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>82058.7614877383</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>88140.399079446</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>94852.2922401861</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>119346.221473026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>95603.9661089566</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>147889.896542409</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>175574.844896949</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>205793.673454091</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>196128.76485089</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>186978.160105416</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>186843.973357169</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>178876.027859734</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>201026.577245476</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>230558.586736442</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>222135.969675</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>229609.727097547</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>241836.463233921</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>400443.019</t>
+          <t>38346249253.7416</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>159748.684</t>
+          <t>16706013656.2207</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>171293.068</t>
+          <t>15894433740.9997</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>175564.396</t>
+          <t>12062697856.8531</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>174715.623</t>
+          <t>15125885253.4912</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>177777.422</t>
+          <t>15796016189.5387</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>170126.99</t>
+          <t>17220815417.5365</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>183341.336</t>
+          <t>19921227974.901</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>179586.988</t>
+          <t>17878198620.1168</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>182376.093</t>
+          <t>25736232295.2908</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>198460.272</t>
+          <t>28211261067.4954</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>193845.386</t>
+          <t>25931346361.9851</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>201335.393</t>
+          <t>22788012497.6328</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>211094.576</t>
+          <t>36356959490.4877</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>222632.673</t>
+          <t>29978126861.4662</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>219844.436</t>
+          <t>34095397708.5909</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>228328.637</t>
+          <t>39666891138.7371</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>221567.196</t>
+          <t>41239053870.2799</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>238960.696</t>
+          <t>42003772536.4505</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>234290.15</t>
+          <t>32506008721.239</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>224315.049</t>
+          <t>30466353458.5592</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>276364.455</t>
+          <t>30949121701.2674</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>293791.174</t>
+          <t>31435511247.9416</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>263959.634</t>
+          <t>39681134382.5104</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>257941.521</t>
+          <t>32732600871.4241</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>286545.049</t>
+          <t>38126230519.0943</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>301526.123</t>
+          <t>38595654171.6085</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>160644.883</t>
+          <t>553.27667237029</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-24870.244</t>
+          <t>2444.52872178824</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-30795.088</t>
+          <t>3892.98935902046</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-28501.217</t>
+          <t>15915.8102266891</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-33981.239</t>
+          <t>17546.8641040294</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-33487.158</t>
+          <t>26366.3970667922</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-39323.505</t>
+          <t>20981.1995323239</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-41397.884</t>
+          <t>18235.2845564928</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-44035.325</t>
+          <t>19815.0481695826</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-46045.971</t>
+          <t>13564.2155587737</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-47202.77</t>
+          <t>13847.1315054738</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-45180.136</t>
+          <t>22202.7766129102</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-44497.813</t>
+          <t>18519.0179611873</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-53237.904</t>
+          <t>6608.36711756347</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-47949.677</t>
+          <t>15771.7757809361</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-45485.336</t>
+          <t>14131.3087909706</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>-41719.771</t>
+          <t>20776.9749724446</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>-40200.173</t>
+          <t>-3671.44212812541</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>-32977.008</t>
+          <t>-7145.5216177934</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>97708.111</t>
+          <t>-6535.07959177908</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>95205.135</t>
+          <t>3821.23253453952</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>111099.72</t>
+          <t>8171.05994221479</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>117822.911</t>
+          <t>11620.1870074508</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>115894.177</t>
+          <t>-12269.4399153337</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>113474.093</t>
+          <t>-6388.94738767113</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>127061.319</t>
+          <t>-5862.24860553668</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>134139.702</t>
+          <t>-4973.66538060948</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>356919.936</t>
+          <t>21678003615.0096</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>177677.661</t>
+          <t>18650010430.3928</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>193600.965</t>
+          <t>23731491040.3235</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>185464.456</t>
+          <t>46324647013.6639</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>191716.885</t>
+          <t>33056137771.2753</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>181439.833</t>
+          <t>25901460205.761</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>195043.329</t>
+          <t>32113701611.7303</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>208239.198</t>
+          <t>26877750605.8594</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>213510.415</t>
+          <t>21847005224.8704</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>205853.477</t>
+          <t>13327571944.5592</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>228832.192</t>
+          <t>14604299354.7012</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>238570.186</t>
+          <t>19254126884.1407</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>230092.542</t>
+          <t>15831573625.8888</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>237705.958</t>
+          <t>7899072186.46472</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>268656.96</t>
+          <t>11654840720.3417</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>254849.781</t>
+          <t>4282546894.80879</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>258871.839</t>
+          <t>2048476980.70024</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>240876.762</t>
+          <t>288610236.387982</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>250181.69</t>
+          <t>-652892541.600712</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>255492.061</t>
+          <t>8027544146.65316</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>222642.697</t>
+          <t>4256677533.74757</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>273577.186</t>
+          <t>6204203039.15613</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>285748.932</t>
+          <t>12131187334.8209</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>306075.788</t>
+          <t>7644459274.72256</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>289989.746</t>
+          <t>8270073810.72898</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>329884.262</t>
+          <t>6640992897.71593</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>347139.516</t>
+          <t>7004392457.8105</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>67091.5846209843</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>74875.0854821416</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>75958.3749076705</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>35350.1163212971</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>53835.9812916107</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>64578.2016972852</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>64329.5363611182</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>70618.3266669635</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>78778.7276045813</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>72750.4439220937</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.007</t>
+          <t>80129.6579260605</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.243</t>
+          <t>92391.1192977188</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>104081.734757218</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.338</t>
+          <t>119546.851136625</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>148040.957801627</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.873</t>
+          <t>204877.723741087</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>3.041</t>
+          <t>205927.911288645</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.123</t>
+          <t>246677.743566537</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>3.153</t>
+          <t>203409.447266047</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>3.308</t>
+          <t>210780.763320579</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>3.219</t>
+          <t>247878.146973674</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>259292.081433034</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>3.933</t>
+          <t>278972.434798375</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4.094</t>
+          <t>272852.157225398</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>4.104</t>
+          <t>313469.533189888</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>4.447</t>
+          <t>333600.730935474</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4.592</t>
+          <t>345457.914732384</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>228038.333</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>106272.027</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>112832.836</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>112953.72</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>113825.211</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>115215.534</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>115277.645</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>118344.023</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>115578.923</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>119134.951</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>126710.162</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>128136.92</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>127294.622</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>130529.358</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>138820.51</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>134405.533</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>138178.658</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>128569.672</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>140511.15</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>139162.173</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>130091.844</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>160466.748</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>171113.742</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>180943.453</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>174573.479</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>195743.908</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>206254.431</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>70340.0321901061</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>81101.0468317506</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>83956.4083973361</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>39193.497651996</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>58564.8219745584</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>72501.046511623</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>71528.9169857739</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>81618.0113548565</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>89947.3004020606</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>87350.6694412581</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>93586.870812827</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>123821.007512098</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>126042.033508475</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>139837.352629988</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>165787.759881353</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>238310.467519986</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>250302.63880804</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>292687.494455779</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.771</t>
+          <t>257587.858408676</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>257646.142322582</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1.881</t>
+          <t>298650.316321967</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>332037.198144167</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2.355</t>
+          <t>339245.512684939</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2.421</t>
+          <t>335166.216594092</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>384732.880950686</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>408032.154760258</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2.728</t>
+          <t>430059.685493065</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>77019.678</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>29593.099</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>31219.992</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>20965.016</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>26247.402</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>31943.919</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>29438.396</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>30072.574</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>28279.497</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>37835.991</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>39308.054</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>38252.403</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>38667.411</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>41539.573</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>40593.022</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>43806.459</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>40707.363</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>42067.203</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>41010.112</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>38641.848</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>42851.005</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>57600.527</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>58629.818</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>62887.281</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>62070.3</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>70799.653</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>73082.66</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>108.58</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-184.04</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-198.64</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-235.95</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-229.47</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-204.83</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-233.58</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-237.66</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-255.71</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-221.7</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-220.08</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-218.11</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-215.08</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-228.16</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-218.12</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-203.83</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-202.49</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-195.56</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-180.41</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>152.86</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>122.18</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>92.88</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>100.96</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>84.29</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>82.82</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>79.47</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>83.55</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>252.032</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>64.683</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>71.106</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>141.808</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>102.165</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>76.396</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80.798</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>74.895</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>183.503</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>75.741</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>86.205</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>63.304</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>55.338</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>52.281</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>47.535</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>32.504</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>30.55</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>27.509</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>31.552</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>13156.167</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>11233.285</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>11827.809</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>455.36</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>500.182</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>430.751</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>458.635</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>459.66</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>117563.318464251</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>138832.619561494</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>144288.351485837</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>67027.9341874676</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>104749.746088879</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>132762.267174648</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>133021.816688166</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>155549.926456561</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>148121.112446631</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>154230.106709949</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>175787.314587461</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>229518.094400298</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>246761.311058154</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>269207.053040112</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>287587.71640055</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>398413.75971987</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>470865.258127767</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>506987.273658618</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>516959.359208386</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>500167.097121036</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>575244.445981802</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>622720.337011542</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>676454.942613188</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>664829.90354811</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>741981.55574066</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>773839.052617758</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>815166.091928054</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>160644882758.964</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-24870243999.9623</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-30795087999.906</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-28501216999.9436</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-33981238999.9296</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-33487158000.0511</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-39323505000.119</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-41397884000.0129</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-44035325000.1183</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-46045971000.0686</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>-47202770000.0392</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-45180135999.9509</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-44497812999.9388</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>-53237903999.9777</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-47949677000.0199</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>-45485336000.0432</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-41719770999.9957</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>-40200173000.0135</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>-32977008000.0858</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>97708111258.489</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>95205135220.2527</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>111099720091.216</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>117822910751.485</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>115894177034.354</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>113474092730.146</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>127061319387.173</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>134139702391.264</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>400443019322.474</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>159748684000.038</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>171293068000.021</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>175564395999.99</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>174715622999.979</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>177777421999.999</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>170126989999.989</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>183341335999.988</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>179586987999.981</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>182376093000.008</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>198460271999.985</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>193845385999.993</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>201335393000.016</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>211094576000.11</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>222632673000.011</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>219844436000.05</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>228328637000.004</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>221567196000.042</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>238960695999.902</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>234290150475.847</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>224315049315.831</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>276364455487.317</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>293791173590.185</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>263959634319.968</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>257941521206.767</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>286545049389.112</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>301526122675.271</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>228038333303.144</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>106272026601.154</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>112832836307.25</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>112953720078.596</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>113825210959.758</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>115215534043.087</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>115277645284.576</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>118344023129.663</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>115578923322.908</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>119134950928.608</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>126710162395.147</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>128136920328.945</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>127294621570.01</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>130529357636.026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>138820510293.872</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>134405533004.719</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>138178658241.367</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>128569672190.384</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>140511149742.265</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>139162172815.572</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>130091843740.597</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>160466747527.588</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>171113742096.898</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>180943453061.026</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>174573479232.426</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>195743908479.826</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>206254430976.033</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>185240906.763822</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>80099900.0000084</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>85691499.9999908</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>86943600.00001</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>87672099.9999858</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>88672899.9999859</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>85797399.9999813</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>90798900.0000315</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>89890699.9999751</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>91221600.0000023</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>96949699.9999861</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>95355299.999987</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>98016799.9999797</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>98831400.0000127</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>104641299.999987</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>107068600.000009</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>109587900</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>104269400.000007</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>113009799.999992</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>111078885.887917</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>104771020.362046</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>129916986.325096</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>138068201.881693</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>127867912.625199</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>124244786.279616</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>138277831.747675</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>145559338.64777</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>71506040.8998303</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>31865800.0000167</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>33173700.0000093</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>34526999.9999903</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>33342999.9999874</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>34088599.9999662</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>31281099.9999747</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>33666500.0000277</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>32679699.999994</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>32706900.000007</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>35326499.9999968</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>34961199.9999884</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>36656300.0000244</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>35428700.0000104</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>39921999.999921</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>41050600.0000193</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>43109499.9999721</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>40647499.9999953</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>47081899.9999954</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>44266440.102038</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>42684362.7990941</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>49865641.3007077</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>52814337.2734153</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>52403530.553433</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>51112296.0590308</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>57265212.3228809</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>60435094.7544518</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>400443019322.474</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>159748684000.038</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>171293068000.021</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>175564395999.99</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>174715622999.979</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>177777421999.999</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>170126989999.989</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>183341335999.988</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>179586987999.981</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>182376093000.008</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>198460271999.985</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>193845385999.993</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>201335393000.016</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>211094576000.11</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>222632673000.011</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>219844436000.05</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>228328637000.004</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>221567196000.042</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>238960695999.902</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>234290150475.847</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>224315049315.831</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>276364455487.317</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>293791173590.185</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>263959634319.968</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>257941521206.767</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>286545049389.112</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>301526122675.271</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>160644882758.964</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-24870243999.9623</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-30795087999.906</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-28501216999.9436</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-33981238999.9296</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-33487158000.0511</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-39323505000.119</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-41397884000.0129</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>-44035325000.1183</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-46045971000.0686</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>-47202770000.0392</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-45180135999.9509</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>-44497812999.9388</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>-53237903999.9777</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>-47949677000.0199</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>-45485336000.0432</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>-41719770999.9957</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>-40200173000.0135</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>-32977008000.0858</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>97708111258.489</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>95205135220.2527</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>111099720091.216</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>117822910751.485</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>115894177034.354</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>113474092730.146</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>127061319387.173</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>134139702391.264</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>397558.900243698</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>456996.158245053</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>492929.595634275</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>212470.898176162</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>330807.010936607</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>412150.500834354</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>416508.736220913</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>481093.55034888</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>484834.675107943</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>481252.711431132</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>522204.004200978</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>661104.447467581</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>706298.983302735</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>777632.075869479</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>880260.399535857</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1195930.61259469</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1364457.34216535</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1534107.92233827</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1474243.92213543</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1443050.53198691</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1633430.96177407</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1755271.38391843</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1852281.93456657</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1834765.16996602</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2050884.22225146</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>2159704.06976427</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2301750.97193893</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>95934.0670913138</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>108567.009510986</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>118558.577909264</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>50591.2868739386</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>76728.1000630814</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>91906.7797516557</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>92249.1684480023</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>104636.016967952</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>112851.921509286</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>105402.832955366</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>113146.980905888</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>135587.204229629</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>149800.091128433</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>167006.452380209</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>198855.189593922</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>274261.958858071</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>286747.178976284</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>336727.209283955</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>294493.848730857</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>291742.745753372</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>341086.197406537</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>371540.361266656</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>385283.339111425</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>377410.407806283</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>438692.241271152</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>466718.519378898</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>490223.018781063</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
